--- a/data/lotto_history.xlsx
+++ b/data/lotto_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1235"/>
+  <dimension ref="A1:I1236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38597,6 +38597,37 @@
         <v>27</v>
       </c>
     </row>
+    <row r="1236">
+      <c r="A1236" t="n">
+        <v>1235</v>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>20260801</t>
+        </is>
+      </c>
+      <c r="C1236" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1236" t="n">
+        <v>15</v>
+      </c>
+      <c r="G1236" t="n">
+        <v>39</v>
+      </c>
+      <c r="H1236" t="n">
+        <v>43</v>
+      </c>
+      <c r="I1236" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/lotto_history.xlsx
+++ b/data/lotto_history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SmartLottoAI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:101_{084CEC11-A353-4AAD-9E05-F5C38CBFCC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915332A8-3660-4ED4-9017-653A3AD50A9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="8040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4008,8 +4008,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1236"/>
+  <dimension ref="A1:I1240"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -39763,6 +39766,122 @@
       </c>
       <c r="I1236">
         <v>20</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1237">
+        <v>1236</v>
+      </c>
+      <c r="B1237">
+        <v>20260808</v>
+      </c>
+      <c r="C1237">
+        <v>12</v>
+      </c>
+      <c r="D1237">
+        <v>18</v>
+      </c>
+      <c r="E1237">
+        <v>21</v>
+      </c>
+      <c r="F1237">
+        <v>29</v>
+      </c>
+      <c r="G1237">
+        <v>34</v>
+      </c>
+      <c r="H1237">
+        <v>38</v>
+      </c>
+      <c r="I1237">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1238">
+        <v>1237</v>
+      </c>
+      <c r="B1238">
+        <v>20260815</v>
+      </c>
+      <c r="C1238">
+        <v>10</v>
+      </c>
+      <c r="D1238">
+        <v>20</v>
+      </c>
+      <c r="E1238">
+        <v>23</v>
+      </c>
+      <c r="F1238">
+        <v>34</v>
+      </c>
+      <c r="G1238">
+        <v>37</v>
+      </c>
+      <c r="H1238">
+        <v>40</v>
+      </c>
+      <c r="I1238">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1239">
+        <v>1238</v>
+      </c>
+      <c r="B1239">
+        <v>20260822</v>
+      </c>
+      <c r="C1239">
+        <v>2</v>
+      </c>
+      <c r="D1239">
+        <v>13</v>
+      </c>
+      <c r="E1239">
+        <v>18</v>
+      </c>
+      <c r="F1239">
+        <v>32</v>
+      </c>
+      <c r="G1239">
+        <v>38</v>
+      </c>
+      <c r="H1239">
+        <v>42</v>
+      </c>
+      <c r="I1239">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1240">
+        <v>1239</v>
+      </c>
+      <c r="B1240">
+        <v>20260829</v>
+      </c>
+      <c r="C1240">
+        <v>11</v>
+      </c>
+      <c r="D1240">
+        <v>13</v>
+      </c>
+      <c r="E1240">
+        <v>22</v>
+      </c>
+      <c r="F1240">
+        <v>32</v>
+      </c>
+      <c r="G1240">
+        <v>33</v>
+      </c>
+      <c r="H1240">
+        <v>36</v>
+      </c>
+      <c r="I1240">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
